--- a/docs/oc-mensuales/administracion-y-entrega-de-beneficios/ago-2025.xlsx
+++ b/docs/oc-mensuales/administracion-y-entrega-de-beneficios/ago-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC ago-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC ago-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6832,7 +6832,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -6893,7 +6893,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -7320,7 +7320,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -7442,7 +7442,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -7564,7 +7564,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7930,7 +7930,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -8052,7 +8052,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -8113,7 +8113,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -8235,7 +8235,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -8357,7 +8357,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -8479,7 +8479,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -8540,7 +8540,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -8601,7 +8601,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -8662,7 +8662,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -8784,7 +8784,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -8845,7 +8845,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -8967,7 +8967,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -9028,7 +9028,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -9272,7 +9272,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -9287,7 +9287,7 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -9337,7 +9337,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -9398,7 +9398,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -9459,7 +9459,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -9520,7 +9520,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -9642,7 +9642,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -9764,7 +9764,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -9825,7 +9825,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -9886,7 +9886,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -9947,7 +9947,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -10069,7 +10069,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -10130,7 +10130,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -10191,7 +10191,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -10252,7 +10252,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -10313,7 +10313,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -10435,7 +10435,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -10496,7 +10496,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -10557,7 +10557,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -10618,7 +10618,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -10679,7 +10679,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -10740,7 +10740,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -10801,7 +10801,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -10862,7 +10862,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -10984,7 +10984,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -11045,7 +11045,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -11106,7 +11106,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -11167,7 +11167,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -11228,7 +11228,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -11289,7 +11289,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -11350,7 +11350,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -11411,7 +11411,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -11472,7 +11472,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -11594,7 +11594,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -11655,7 +11655,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -11899,7 +11899,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -11960,7 +11960,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -12021,7 +12021,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -12082,7 +12082,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -12143,7 +12143,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -12265,7 +12265,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -12326,7 +12326,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -12387,7 +12387,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -12448,7 +12448,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -12509,7 +12509,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -12570,7 +12570,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -12631,7 +12631,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -12692,7 +12692,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -12753,7 +12753,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -12814,7 +12814,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -12875,7 +12875,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -12936,7 +12936,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -12997,7 +12997,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -13058,7 +13058,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -13119,7 +13119,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -13180,7 +13180,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -13241,7 +13241,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -13302,7 +13302,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -13363,7 +13363,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -13424,7 +13424,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -13485,7 +13485,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -13546,7 +13546,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -13607,7 +13607,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -13668,7 +13668,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -13729,7 +13729,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -13790,7 +13790,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -13851,7 +13851,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -13912,7 +13912,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -13973,7 +13973,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -14034,7 +14034,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -14095,7 +14095,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -14156,7 +14156,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -14217,7 +14217,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -14278,7 +14278,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -14339,7 +14339,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -14400,7 +14400,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -14461,7 +14461,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -14522,7 +14522,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -14583,7 +14583,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -14705,7 +14705,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -14766,7 +14766,7 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -14827,7 +14827,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -14888,7 +14888,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -14949,7 +14949,7 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -15010,7 +15010,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -15071,7 +15071,7 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -15132,7 +15132,7 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -15193,7 +15193,7 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -15315,7 +15315,7 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -15437,7 +15437,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -15559,7 +15559,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -15620,7 +15620,7 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -15681,7 +15681,7 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -15742,7 +15742,7 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -15803,7 +15803,7 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
@@ -15864,7 +15864,7 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -15925,7 +15925,7 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -15986,7 +15986,7 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -16047,7 +16047,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -16108,7 +16108,7 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -16169,7 +16169,7 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
@@ -16230,7 +16230,7 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -16291,7 +16291,7 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -16352,7 +16352,7 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -16413,7 +16413,7 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
@@ -16596,7 +16596,7 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
@@ -16718,7 +16718,7 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -16779,7 +16779,7 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -16840,7 +16840,7 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
@@ -16901,7 +16901,7 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -16962,7 +16962,7 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -17023,7 +17023,7 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -17084,7 +17084,7 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -17145,7 +17145,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -17206,7 +17206,7 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -17267,7 +17267,7 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -17328,7 +17328,7 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
@@ -17389,7 +17389,7 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -17511,7 +17511,7 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -17633,7 +17633,7 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -17694,7 +17694,7 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -17755,7 +17755,7 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -17816,7 +17816,7 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -17877,7 +17877,7 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -17938,7 +17938,7 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -17999,7 +17999,7 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -18060,7 +18060,7 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -18121,7 +18121,7 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
@@ -18182,7 +18182,7 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -18243,7 +18243,7 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -18304,7 +18304,7 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -18365,7 +18365,7 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -18426,7 +18426,7 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -18487,7 +18487,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -18548,7 +18548,7 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -18609,7 +18609,7 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -18670,7 +18670,7 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -18731,7 +18731,7 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -18792,7 +18792,7 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -18853,7 +18853,7 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -18914,7 +18914,7 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -18975,7 +18975,7 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -19036,7 +19036,7 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -19097,7 +19097,7 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -19158,7 +19158,7 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -19219,7 +19219,7 @@
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -19280,7 +19280,7 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -19341,7 +19341,7 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -19402,7 +19402,7 @@
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -19463,7 +19463,7 @@
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">

--- a/docs/oc-mensuales/administracion-y-entrega-de-beneficios/ago-2025.xlsx
+++ b/docs/oc-mensuales/administracion-y-entrega-de-beneficios/ago-2025.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M312"/>
+  <dimension ref="A1:M313"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -562,7 +562,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1017,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1082,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1147,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1212,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1277,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1342,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1407,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1472,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1537,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1602,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1667,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1732,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1797,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1862,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1927,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1992,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2057,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2122,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2187,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2252,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2317,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2382,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2447,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2512,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2577,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2642,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2707,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2772,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2837,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2902,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2967,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +3032,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3097,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3162,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3227,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3292,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3357,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3422,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3487,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3552,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3617,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3682,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3747,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3812,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3877,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3942,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +4007,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +4072,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4137,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4202,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4267,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4332,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4397,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4462,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4527,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4592,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4657,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4722,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4787,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4852,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4917,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4982,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +5047,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +5112,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5177,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5242,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5307,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5372,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5437,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5198,7 +5502,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5567,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5632,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5697,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5442,7 +5762,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5503,7 +5827,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5892,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5625,7 +5957,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +6022,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +6087,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +6152,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +6217,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5930,7 +6282,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6347,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6412,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6477,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6542,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6607,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6296,7 +6672,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6357,7 +6737,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6802,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6867,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6540,7 +6932,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6997,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6662,7 +7062,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6723,7 +7127,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6784,7 +7192,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6845,7 +7257,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6906,7 +7322,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6967,7 +7387,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7028,7 +7452,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7089,7 +7517,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7150,7 +7582,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7211,7 +7647,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7272,7 +7712,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7333,7 +7777,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7394,7 +7842,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7455,7 +7907,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7516,7 +7972,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7577,7 +8037,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7638,7 +8102,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7699,7 +8167,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7760,7 +8232,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7821,7 +8297,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7882,7 +8362,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7943,7 +8427,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8004,7 +8492,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8065,7 +8557,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8126,7 +8622,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8187,7 +8687,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8248,7 +8752,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8309,7 +8817,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8370,7 +8882,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8431,7 +8947,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8492,7 +9012,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8553,7 +9077,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8614,7 +9142,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8675,7 +9207,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8736,7 +9272,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8797,7 +9337,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8858,7 +9402,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8919,7 +9467,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8980,7 +9532,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9041,7 +9597,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9102,7 +9662,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9163,7 +9727,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9224,7 +9792,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9350,7 +9922,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9411,7 +9987,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9472,7 +10052,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9533,7 +10117,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9594,7 +10182,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9655,7 +10247,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9716,7 +10312,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9777,7 +10377,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9838,7 +10442,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9899,7 +10507,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9960,7 +10572,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10021,7 +10637,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10082,7 +10702,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10143,7 +10767,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10204,7 +10832,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10265,7 +10897,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10326,7 +10962,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10387,7 +11027,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10448,7 +11092,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10509,7 +11157,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10570,7 +11222,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10631,7 +11287,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10692,7 +11352,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10753,7 +11417,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10814,7 +11482,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10875,7 +11547,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10936,7 +11612,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10997,7 +11677,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11058,7 +11742,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11119,7 +11807,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11180,7 +11872,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11241,7 +11937,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11302,7 +12002,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11363,7 +12067,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11424,7 +12132,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11485,7 +12197,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11546,7 +12262,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11607,7 +12327,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11668,7 +12392,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11729,7 +12457,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11790,7 +12522,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11851,7 +12587,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11912,7 +12652,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11973,7 +12717,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12034,7 +12782,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12095,7 +12847,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12156,7 +12912,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12217,7 +12977,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12278,7 +13042,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12339,7 +13107,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12400,7 +13172,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12461,7 +13237,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12522,7 +13302,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12583,7 +13367,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12644,7 +13432,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12705,7 +13497,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12766,7 +13562,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12827,7 +13627,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12888,7 +13692,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12901,7 +13709,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>1388974-200-CM25</t>
+          <t>1079694-273-CM25</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -12921,22 +13729,22 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>71.146.000-4</t>
+          <t>60.505.523-0</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE EDUCACION Y SERVICIOS RAMON FREIRE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -12949,14 +13757,18 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>15300.45</v>
+        <v>20672.29</v>
       </c>
     </row>
     <row r="206">
@@ -13010,7 +13822,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13071,7 +13887,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13084,7 +13904,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>1079694-273-CM25</t>
+          <t>1388974-200-CM25</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -13104,22 +13924,22 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>60.505.523-0</t>
+          <t>71.146.000-4</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>CORP MUNICIPAL DE EDUCACION Y SERVICIOS RAMON FREIRE</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -13132,14 +13952,18 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>20672.29</v>
+        <v>15300.45</v>
       </c>
     </row>
     <row r="209">
@@ -13193,7 +14017,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13254,7 +14082,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13267,7 +14099,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>1079639-751-CM25</t>
+          <t>622-472-SE25</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -13292,17 +14124,17 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>60.805.000-0</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>TESORERIA GENERAL DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -13315,20 +14147,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>56484.57</v>
+        <v>87224.00999999999</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2887-180-CM25</t>
+          <t>1079639-751-CM25</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -13348,17 +14184,17 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>69.210.600-8</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUYEHUE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -13376,20 +14212,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>7231.05</v>
+        <v>56484.57</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>1391-1741-CM25</t>
+          <t>2887-180-CM25</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -13404,27 +14244,27 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>61.004.051-9</t>
+          <t>69.210.600-8</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>I MUNICIPALIDAD DE PUYEHUE</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -13437,20 +14277,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>3613.35</v>
+        <v>7231.05</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2981-1196-CM25</t>
+          <t>1391-1741-CM25</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -13475,17 +14319,17 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>61.004.051-9</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -13498,20 +14342,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>61470.12</v>
+        <v>3613.35</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>973168-11-CM25</t>
+          <t>2981-1196-CM25</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -13536,17 +14384,17 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>60.803.435-8</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -13559,20 +14407,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>2611.94</v>
+        <v>61470.12</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>1347-47-CM25</t>
+          <t>973168-11-CM25</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -13597,17 +14449,17 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>61.002.492-0</t>
+          <t>60.803.435-8</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
+          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -13620,20 +14472,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>5270.43</v>
+        <v>2611.94</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>1019-414-CM25</t>
+          <t>1347-47-CM25</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -13653,22 +14509,22 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.002.492-0</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -13681,20 +14537,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>999.3</v>
+        <v>5270.43</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>1019-413-CM25</t>
+          <t>1019-414-CM25</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -13742,20 +14602,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>2879.47</v>
+        <v>999.3</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>1965-521-CM25</t>
+          <t>1019-413-CM25</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -13775,22 +14639,22 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>61.004.054-3</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -13803,20 +14667,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>4119.91</v>
+        <v>2879.47</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>1057534-1030-CM25</t>
+          <t>1965-521-CM25</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -13841,17 +14709,17 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>61.607.602-7</t>
+          <t>61.004.054-3</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD OSORNO HOSPITAL PURRANQUE</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -13864,20 +14732,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>20647.72</v>
+        <v>4119.91</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2080-31683-CM25</t>
+          <t>1057534-1030-CM25</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -13902,17 +14774,17 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>61.602.138-9</t>
+          <t>61.607.602-7</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
+          <t>SERVICIO DE SALUD OSORNO HOSPITAL PURRANQUE</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -13925,20 +14797,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>10840.05</v>
+        <v>20647.72</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>1057370-2396-CM25</t>
+          <t>2186-815-CM25</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -13963,12 +14839,12 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>61.602.040-4</t>
+          <t>61.606.607-2</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>HOSPITAL PSIQUIATRICO DR. PHILIPPE PINEL PUTAENDO</t>
+          <t>HOSPITAL GERIATRICO LA PAZ DE LA TARDE</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -13986,20 +14862,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>24491.68</v>
+        <v>3501.34</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>3385-162-CM25</t>
+          <t>1057370-2396-CM25</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -14024,17 +14904,17 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>61.101.023-0</t>
+          <t>61.602.040-4</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>HOSPITAL PSIQUIATRICO DR. PHILIPPE PINEL PUTAENDO</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -14047,20 +14927,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>4129.54</v>
+        <v>24491.68</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>1391-1720-CM25</t>
+          <t>3385-162-CM25</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -14085,12 +14969,12 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>61.004.051-9</t>
+          <t>61.101.023-0</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -14108,20 +14992,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>8775.280000000001</v>
+        <v>4129.54</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>1391-1717-CM25</t>
+          <t>1391-1720-CM25</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -14169,20 +15057,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>237.45</v>
+        <v>8775.280000000001</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>952946-189-CM25</t>
+          <t>1391-1717-CM25</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -14207,17 +15099,17 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>61.004.051-9</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -14230,20 +15122,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>2064.77</v>
+        <v>237.45</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>1057499-404-CM25</t>
+          <t>952946-189-CM25</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -14268,17 +15164,17 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>61.608.108-K</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD SUR UNIDAD HOSPITALARI</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -14291,20 +15187,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>20647.72</v>
+        <v>2064.77</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2186-815-CM25</t>
+          <t>1057499-404-CM25</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -14329,17 +15229,17 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>61.606.607-2</t>
+          <t>61.608.108-K</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>HOSPITAL GERIATRICO LA PAZ DE LA TARDE</t>
+          <t>SERVICIO DE SALUD SUR UNIDAD HOSPITALARI</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -14352,20 +15252,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>3501.34</v>
+        <v>20647.72</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>1953-1690-CM25</t>
+          <t>2080-31683-CM25</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -14380,27 +15284,27 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>61.004.024-1</t>
+          <t>61.602.138-9</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -14413,20 +15317,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>310.69</v>
+        <v>10840.05</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>1978-972-CM25</t>
+          <t>1953-1690-CM25</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -14451,17 +15359,17 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>61.606.900-4</t>
+          <t>61.004.024-1</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -14474,20 +15382,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>49266.19</v>
+        <v>310.69</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>3515-464-CM25</t>
+          <t>1978-972-CM25</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -14512,17 +15424,17 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>69.060.300-4</t>
+          <t>61.606.900-4</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CALERA</t>
+          <t>SERVICIO DE SALUD DEL MAULE</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -14535,20 +15447,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>1465.54</v>
+        <v>49266.19</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>1157285-14-CM25</t>
+          <t>3515-464-CM25</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -14573,17 +15489,17 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>62.000.860-5</t>
+          <t>69.060.300-4</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA PARA LAS FUERZAS ARMADAS</t>
+          <t>I MUNICIPALIDAD DE LA CALERA</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -14596,20 +15512,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>5382.98</v>
+        <v>1465.54</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>3515-462-CM25</t>
+          <t>1157285-14-CM25</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -14634,17 +15554,17 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>69.060.300-4</t>
+          <t>62.000.860-5</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CALERA</t>
+          <t>SUBSECRETARIA PARA LAS FUERZAS ARMADAS</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -14657,20 +15577,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>1465.54</v>
+        <v>5382.98</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>1620-245-CM25</t>
+          <t>3515-462-CM25</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -14690,22 +15614,22 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>61.602.146-k</t>
+          <t>69.060.300-4</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE CHIMBARONGO</t>
+          <t>I MUNICIPALIDAD DE LA CALERA</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -14718,20 +15642,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>12446.46</v>
+        <v>1465.54</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>2594-808-CM25</t>
+          <t>1620-245-CM25</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -14751,22 +15679,22 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>73.568.600-3</t>
+          <t>61.602.146-k</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCON</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE CHIMBARONGO</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -14779,20 +15707,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>303.02</v>
+        <v>12446.46</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>1079454-482-CM25</t>
+          <t>2594-808-CM25</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -14812,22 +15744,22 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>73.568.600-3</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE CONCON</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -14840,20 +15772,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>41027.41</v>
+        <v>303.02</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>585-179-CM25</t>
+          <t>1079454-482-CM25</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -14873,22 +15809,22 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>82.174.900-k</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>SERVICIO DE COOPERACION TECNICA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -14901,20 +15837,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>28750.71</v>
+        <v>41027.41</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>1274667-449-CM25</t>
+          <t>585-179-CM25</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -14934,22 +15874,22 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>62.000.940-7</t>
+          <t>82.174.900-k</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
+          <t>SERVICIO DE COOPERACION TECNICA</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -14962,20 +15902,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>12446.2</v>
+        <v>28750.71</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>1108338-204-CM25</t>
+          <t>1274667-449-CM25</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -14990,7 +15934,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -15000,17 +15944,17 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>69.287.570-2</t>
+          <t>62.000.940-7</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL N°2 DE LOS ANDES</t>
+          <t>CENTRO DE SALUD FAMILIAR PUERTO AYSÉN</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -15023,20 +15967,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>10909.06</v>
+        <v>12446.2</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>2429-2496-CM25</t>
+          <t>1108338-204-CM25</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -15056,22 +16004,22 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>69.287.570-2</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>CONSULTORIO GENERAL N°2 DE LOS ANDES</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -15084,20 +16032,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>30359</v>
+        <v>10909.06</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>1079689-277-CM25</t>
+          <t>2429-2496-CM25</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -15117,22 +16069,22 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>60.505.627-K</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -15145,20 +16097,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>17828.72</v>
+        <v>30359</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2374-157-CM25</t>
+          <t>1079689-277-CM25</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -15183,17 +16139,17 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>61.608.001-6</t>
+          <t>60.505.627-K</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RECOLETA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -15206,20 +16162,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>10961.34</v>
+        <v>17828.72</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>586269-62-CM25</t>
+          <t>2374-157-CM25</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -15239,17 +16199,17 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>60.101.000-3</t>
+          <t>61.608.001-6</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>SECRETARIA GENERAL DE GOBIERNO</t>
+          <t>I MUNICIPALIDAD DE RECOLETA</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -15267,20 +16227,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>519.47</v>
+        <v>10961.34</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>617807-7887-CM25</t>
+          <t>586269-62-CM25</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -15305,17 +16269,17 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>61.602.036-6</t>
+          <t>60.101.000-3</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>SERV NAC SALUD HOSPITAL DE LOS ANDES</t>
+          <t>SECRETARIA GENERAL DE GOBIERNO</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -15328,20 +16292,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>17264.65</v>
+        <v>519.47</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>507428-3527-CM25</t>
+          <t>617807-7887-CM25</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -15361,22 +16329,22 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>61.979.210-6</t>
+          <t>61.602.036-6</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>SERV NAC SALUD HOSPITAL DE LOS ANDES</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -15389,20 +16357,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>24675.07</v>
+        <v>17264.65</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>4337-394-CM25</t>
+          <t>507428-3527-CM25</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -15427,17 +16399,17 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>69.180.400-3</t>
+          <t>61.979.210-6</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENAICO</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -15450,20 +16422,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>457.14</v>
+        <v>24675.07</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>1403-4067-CM25</t>
+          <t>4337-394-CM25</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -15488,17 +16464,17 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>61.004.101-9</t>
+          <t>69.180.400-3</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>I MUNICIPALIDAD DE RENAICO</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -15511,20 +16487,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>519.48</v>
+        <v>457.14</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>1552-5033-CM25</t>
+          <t>1403-4067-CM25</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -15549,17 +16529,17 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>61.004.101-9</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -15572,20 +16552,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>34285.36</v>
+        <v>519.48</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>3474-629-CM25</t>
+          <t>1552-5033-CM25</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -15610,17 +16594,17 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>61.979.960-7</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -15633,20 +16617,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>656.36</v>
+        <v>34285.36</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>4337-393-CM25</t>
+          <t>3474-629-CM25</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -15671,17 +16659,17 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>69.180.400-3</t>
+          <t>61.979.960-7</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENAICO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -15694,20 +16682,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>7927.4</v>
+        <v>656.36</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>2102-756-CM25</t>
+          <t>4337-393-CM25</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -15732,17 +16724,17 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>61.602.212-1</t>
+          <t>69.180.400-3</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LEBU</t>
+          <t>I MUNICIPALIDAD DE RENAICO</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -15755,20 +16747,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>35283.37</v>
+        <v>7927.4</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>1057461-7556-CM25</t>
+          <t>2102-756-CM25</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -15793,17 +16789,17 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>61.606.913-6</t>
+          <t>61.602.212-1</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LEBU</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
@@ -15816,20 +16812,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L252" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>28726.76</v>
+        <v>35283.37</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>3387-159-CM25</t>
+          <t>1057461-7556-CM25</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -15854,17 +16854,17 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>61.101.008-7</t>
+          <t>61.606.913-6</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -15877,20 +16877,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>872.72</v>
+        <v>28726.76</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>3474-618-CM25</t>
+          <t>3387-159-CM25</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -15915,12 +16919,12 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>61.979.960-7</t>
+          <t>61.101.008-7</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -15938,20 +16942,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>473.76</v>
+        <v>872.72</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>1057531-818-CM25</t>
+          <t>3474-618-CM25</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -15976,17 +16984,17 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>61.602.262-8</t>
+          <t>61.979.960-7</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE RIO NEGRO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -15999,20 +17007,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>12986.88</v>
+        <v>473.76</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>930-254-CM25</t>
+          <t>1057531-818-CM25</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -16037,17 +17049,17 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.602.262-8</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE RIO NEGRO</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -16060,20 +17072,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>365.71</v>
+        <v>12986.88</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>1199-224-CM25</t>
+          <t>930-254-CM25</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -16108,7 +17124,7 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -16121,20 +17137,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>1454.53</v>
+        <v>365.71</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>2085-754-CM25</t>
+          <t>1199-224-CM25</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -16159,17 +17179,17 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>61.602.226-1</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
@@ -16182,20 +17202,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>25099.48</v>
+        <v>1454.53</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>1402-561-CM25</t>
+          <t>2085-754-CM25</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -16220,17 +17244,17 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>61.004.042-K</t>
+          <t>61.602.226-1</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -16243,20 +17267,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>1766.21</v>
+        <v>25099.48</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>1402-562-CM25</t>
+          <t>1402-561-CM25</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -16304,20 +17332,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>11428.45</v>
+        <v>1766.21</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>3950-4261-CM25</t>
+          <t>1402-562-CM25</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -16337,22 +17369,22 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>61.974.600-7</t>
+          <t>61.004.042-K</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>DIRECCION SALUD RURAL</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -16365,20 +17397,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>4564.89</v>
+        <v>11428.45</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>1371-46-CM25</t>
+          <t>3950-4261-CM25</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -16393,27 +17429,27 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>75.971.200-5</t>
+          <t>61.974.600-7</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Comité de Seguros del Agro</t>
+          <t>DIRECCION SALUD RURAL</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
@@ -16426,20 +17462,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>631.33</v>
+        <v>4564.89</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>5911-217-CM25</t>
+          <t>1371-46-CM25</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -16464,12 +17504,12 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>70.819.400-K</t>
+          <t>75.971.200-5</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>TRIBUNAL CONSTITUCIONAL</t>
+          <t>Comité de Seguros del Agro</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -16487,20 +17527,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>9209.700000000001</v>
+        <v>631.33</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>2046-396-CM25</t>
+          <t>5911-217-CM25</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -16525,17 +17569,17 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>61.606.908-k</t>
+          <t>70.819.400-K</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE MOLINA</t>
+          <t>TRIBUNAL CONSTITUCIONAL</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
@@ -16548,20 +17592,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>18837.37</v>
+        <v>9209.700000000001</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>1557-285-CM25</t>
+          <t>2046-396-CM25</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -16586,17 +17634,17 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>61.606.309-k</t>
+          <t>61.606.908-k</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE MOLINA</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
@@ -16609,20 +17657,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>10843.18</v>
+        <v>18837.37</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>1077908-231-CM25</t>
+          <t>1557-285-CM25</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -16647,17 +17699,17 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>62.000.380-8</t>
+          <t>61.606.309-k</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>CENTRO ONCOLOGICO DEL NORTE</t>
+          <t>SERVICIO SALUD ATACAMA HOSPITAL DE HUASCO</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
@@ -16670,20 +17722,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L266" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>32631.08</v>
+        <v>10843.18</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>1402-573-CM25</t>
+          <t>1077908-231-CM25</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -16708,17 +17764,17 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>61.004.042-K</t>
+          <t>62.000.380-8</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>CENTRO ONCOLOGICO DEL NORTE</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -16731,20 +17787,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>1036.26</v>
+        <v>32631.08</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>900-870-CM25</t>
+          <t>1402-573-CM25</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -16769,17 +17829,17 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>61.979.910-0</t>
+          <t>61.004.042-K</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -16792,20 +17852,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>6025.22</v>
+        <v>1036.26</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>598-232-CM25</t>
+          <t>900-870-CM25</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -16830,17 +17894,17 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>61.513.000-1</t>
+          <t>61.979.910-0</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>DIRECCION PREVISION DE CARABINEROS DE CHILE</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
@@ -16853,20 +17917,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>25906.47</v>
+        <v>6025.22</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>652-358-CM25</t>
+          <t>598-232-CM25</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -16891,17 +17959,17 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>61.954.500-1</t>
+          <t>61.513.000-1</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCO</t>
+          <t>DIRECCION PREVISION DE CARABINEROS DE CHILE</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -16914,20 +17982,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>37891.32</v>
+        <v>25906.47</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>1469-2454-CM25</t>
+          <t>652-358-CM25</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -16947,22 +18019,22 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>61.954.500-1</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>SERVICIO DE SALUD ARAUCO</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -16975,20 +18047,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>173.26</v>
+        <v>37891.32</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>976-264-CM25</t>
+          <t>1469-2454-CM25</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -17013,17 +18089,17 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -17036,20 +18112,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>4513.94</v>
+        <v>173.26</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>1623-388-CM25</t>
+          <t>976-264-CM25</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -17069,22 +18149,22 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>61.602.142-7</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PEUMO</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -17097,20 +18177,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>414.51</v>
+        <v>4513.94</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>1391-1736-CM25</t>
+          <t>1623-388-CM25</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -17135,17 +18219,17 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>61.004.051-9</t>
+          <t>61.602.142-7</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PEUMO</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -17158,20 +18242,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr"/>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L274" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>238.33</v>
+        <v>414.51</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>1623-389-CM25</t>
+          <t>1391-1736-CM25</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -17196,17 +18284,17 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>61.602.142-7</t>
+          <t>61.004.051-9</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PEUMO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -17219,20 +18307,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr"/>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L275" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>414.51</v>
+        <v>238.33</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>585-180-CM25</t>
+          <t>1623-389-CM25</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -17252,22 +18344,22 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>82.174.900-k</t>
+          <t>61.602.142-7</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>SERVICIO DE COOPERACION TECNICA</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PEUMO</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -17280,20 +18372,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr"/>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L276" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>322.9</v>
+        <v>414.51</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>585-181-CM25</t>
+          <t>585-180-CM25</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -17341,20 +18437,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr"/>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L277" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>24431.29</v>
+        <v>322.9</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>952946-192-CM25</t>
+          <t>585-181-CM25</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -17374,22 +18474,22 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>65.127.823-6</t>
+          <t>82.174.900-k</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE COOPERACION TECNICA</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -17402,20 +18502,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr"/>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L278" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>2072.52</v>
+        <v>24431.29</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>3399-166-CM25</t>
+          <t>952946-192-CM25</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -17440,7 +18544,7 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>61.946.800-7</t>
+          <t>65.127.823-6</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
@@ -17450,7 +18554,7 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
@@ -17463,7 +18567,11 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr"/>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L279" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17476,7 +18584,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>2170-2943-CM25</t>
+          <t>3399-166-CM25</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -17501,17 +18609,17 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>61.606.606-4</t>
+          <t>61.946.800-7</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>HOSPITAL DE LA FAMILIA Y LA COMUNIDAD SANTO TOMAS DE LIMACHE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -17524,20 +18632,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr"/>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L280" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>18822.6</v>
+        <v>2072.52</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>2170-2944-CM25</t>
+          <t>2170-2943-CM25</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -17585,20 +18697,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>3555.82</v>
+        <v>18822.6</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>1686-18-CM25</t>
+          <t>2170-2944-CM25</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -17623,17 +18739,17 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>60.803.000-k</t>
+          <t>61.606.606-4</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
+          <t>HOSPITAL DE LA FAMILIA Y LA COMUNIDAD SANTO TOMAS DE LIMACHE</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -17646,20 +18762,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr"/>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>2576.14</v>
+        <v>3555.82</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>3951-264-CM25</t>
+          <t>1686-18-CM25</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -17684,12 +18804,12 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>61.974.700-3</t>
+          <t>60.803.000-k</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>CONSULTORIO GENERAL URBANO VICTOR DOMINGO SILVA</t>
+          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -17707,20 +18827,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>7959.24</v>
+        <v>2576.14</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>5349-1739-CM25</t>
+          <t>3951-264-CM25</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -17735,7 +18859,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -17745,17 +18869,17 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.974.700-3</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>CONSULTORIO GENERAL URBANO VICTOR DOMINGO SILVA</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -17768,20 +18892,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr"/>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L284" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>53097.39</v>
+        <v>7959.24</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>950-101-CM25</t>
+          <t>5349-1739-CM25</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -17806,17 +18934,17 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>60.901.007-K</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -17829,20 +18957,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L285" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>367.64</v>
+        <v>53097.39</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>1946-89-CM25</t>
+          <t>950-101-CM25</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -17867,17 +18999,17 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>61.109.000-5</t>
+          <t>60.901.007-K</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>DEFENSA CIVIL DE CHILE</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -17890,20 +19022,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr"/>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L286" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>1249.01</v>
+        <v>367.64</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>950-100-CM25</t>
+          <t>1946-89-CM25</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -17928,17 +19064,17 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>60.901.007-K</t>
+          <t>61.109.000-5</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>DEFENSA CIVIL DE CHILE</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -17951,20 +19087,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr"/>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>81.7</v>
+        <v>1249.01</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>4281-153-CM25</t>
+          <t>950-100-CM25</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -17984,22 +19124,22 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>69.191.000-8</t>
+          <t>60.901.007-K</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CUNCO</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -18012,20 +19152,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L288" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>8507.620000000001</v>
+        <v>81.7</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>889473-1728-CM25</t>
+          <t>4281-153-CM25</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -18045,22 +19189,22 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>61.980.530-5</t>
+          <t>69.191.000-8</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE O'HIGGINS</t>
+          <t>I MUNICIPALIDAD DE CUNCO</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -18073,20 +19217,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr"/>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L289" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>11345.39</v>
+        <v>8507.620000000001</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>1529-322-CM25</t>
+          <t>889473-1728-CM25</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -18111,12 +19259,12 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>61.980.530-5</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>UNIVERSIDAD DE O'HIGGINS</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -18134,20 +19282,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr"/>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L290" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>50935.62</v>
+        <v>11345.39</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>1070329-287-CM25</t>
+          <t>1529-322-CM25</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -18172,17 +19324,17 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>61.980.370-1</t>
+          <t>61.602.140-0</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>CESFAM LIRQUEN</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -18195,20 +19347,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr"/>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L291" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>12954.81</v>
+        <v>50935.62</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>1057540-16900-CM25</t>
+          <t>1070329-287-CM25</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -18233,12 +19389,12 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>61.602.198-2</t>
+          <t>61.980.370-1</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD TALCAHUANO HOSPITAL PENCO-LIRQUEN</t>
+          <t>CESFAM LIRQUEN</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -18256,20 +19412,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L292" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>73556.74000000001</v>
+        <v>12954.81</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>1622-892-CM25</t>
+          <t>1057540-16900-CM25</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -18294,17 +19454,17 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>61.602.141-9</t>
+          <t>61.602.198-2</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
+          <t>SERVICIO SALUD TALCAHUANO HOSPITAL PENCO-LIRQUEN</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -18317,20 +19477,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr"/>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L293" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>23744.63</v>
+        <v>73556.74000000001</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>1288-482-CM25</t>
+          <t>1622-892-CM25</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -18350,22 +19514,22 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>61.608.200-0</t>
+          <t>61.602.141-9</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD METROPOLITANO OCCIDENTE</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -18378,20 +19542,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L294" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>39230.26</v>
+        <v>23744.63</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>1681-686-CM25</t>
+          <t>1288-482-CM25</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -18411,22 +19579,22 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>61.606.917-9</t>
+          <t>61.608.200-0</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+          <t>SERVICIO SALUD METROPOLITANO OCCIDENTE</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -18439,20 +19607,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr"/>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L295" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>46153.62</v>
+        <v>39230.26</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>1681-685-CM25</t>
+          <t>1681-686-CM25</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -18500,20 +19672,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>32450.36</v>
+        <v>46153.62</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>2045-293-CM25</t>
+          <t>1681-685-CM25</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -18538,12 +19714,12 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>61.606.910-1</t>
+          <t>61.606.917-9</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CUREPTO</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -18561,20 +19737,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>7742.82</v>
+        <v>32450.36</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>2035-91-CM25</t>
+          <t>2045-293-CM25</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -18594,22 +19774,22 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>60.511.032-0</t>
+          <t>61.606.910-1</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE CHAÑARAL</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CUREPTO</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -18622,20 +19802,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr"/>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>908.49</v>
+        <v>7742.82</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>1233600-696-CM25</t>
+          <t>2035-91-CM25</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -18650,27 +19834,27 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>70.931.100-K</t>
+          <t>60.511.032-0</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE RENCA</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE CHAÑARAL</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -18683,20 +19867,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr"/>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L299" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>2891.78</v>
+        <v>908.49</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>1057514-423-CM25</t>
+          <t>1233600-696-CM25</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -18721,17 +19909,17 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>61.607.006-1</t>
+          <t>70.931.100-K</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE EL C</t>
+          <t>CORP MUNICIPAL DE RENCA</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -18744,20 +19932,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr"/>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L300" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>13539.37</v>
+        <v>2891.78</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>3922-845-CM25</t>
+          <t>1057514-423-CM25</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -18777,22 +19969,22 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>69.191.500-K</t>
+          <t>61.607.006-1</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLARRICA</t>
+          <t>SERVICIO DE SALUD NUBLE HOSPITAL DE EL C</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -18805,20 +19997,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr"/>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L301" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>589.16</v>
+        <v>13539.37</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>2138-206-CM25</t>
+          <t>3922-845-CM25</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -18838,22 +20034,22 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>61.978.730-7</t>
+          <t>69.191.500-K</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>I MUNICIPALIDAD DE VILLARRICA</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -18866,20 +20062,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr"/>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L302" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>10336.13</v>
+        <v>589.16</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>5312-38-CM25</t>
+          <t>2138-206-CM25</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -18904,17 +20104,17 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>61.008.000-6</t>
+          <t>61.978.730-7</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE MENORES</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -18927,20 +20127,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr"/>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L303" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>1028.28</v>
+        <v>10336.13</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>876-277-CM25</t>
+          <t>5312-38-CM25</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -18965,12 +20169,12 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>60.101.000-3</t>
+          <t>61.008.000-6</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>SECRETARIA GENERAL DE GOBIERNO</t>
+          <t>SERVICIO NACIONAL DE MENORES</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -18988,20 +20192,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K304" t="inlineStr"/>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L304" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>213.75</v>
+        <v>1028.28</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>4291-1656-CM25</t>
+          <t>876-277-CM25</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -19021,22 +20229,22 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>60.101.000-3</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>SECRETARIA GENERAL DE GOBIERNO</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -19049,20 +20257,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr"/>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L305" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>3100.84</v>
+        <v>213.75</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>972135-12-CM25</t>
+          <t>4291-1656-CM25</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -19082,22 +20294,22 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>69.150.400-k</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -19110,20 +20322,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr"/>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L306" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>15598.09</v>
+        <v>3100.84</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>3483-196-CM25</t>
+          <t>972135-12-CM25</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -19148,17 +20364,17 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>65.286.830-4</t>
+          <t>69.150.400-k</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -19171,20 +20387,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr"/>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L307" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>177.78</v>
+        <v>15598.09</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>1099899-156-CM25</t>
+          <t>3483-196-CM25</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -19209,17 +20429,17 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>62.000.630-0</t>
+          <t>65.286.830-4</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>CENTRO SALUD MENTAL COMUNITARIA LOS ANDES</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -19232,20 +20452,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr"/>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L308" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>6415.95</v>
+        <v>177.78</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>1099899-155-CM25</t>
+          <t>1099899-156-CM25</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -19293,20 +20517,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>1252.95</v>
+        <v>6415.95</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>1233600-697-CM25</t>
+          <t>1099899-155-CM25</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -19331,17 +20559,17 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>70.931.100-K</t>
+          <t>62.000.630-0</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE RENCA</t>
+          <t>CENTRO SALUD MENTAL COMUNITARIA LOS ANDES</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -19354,20 +20582,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr"/>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L310" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>5841.98</v>
+        <v>1252.95</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>1057385-367-CM25</t>
+          <t>1233600-697-CM25</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -19392,17 +20624,17 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>61.606.204-2</t>
+          <t>70.931.100-K</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+          <t>CORP MUNICIPAL DE RENCA</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -19415,74 +20647,147 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr"/>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L311" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>19638.65</v>
+        <v>5841.98</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
+          <t>1057385-367-CM25</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>61.606.204-2</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M312" s="2" t="n">
+        <v>19638.65</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
           <t>3632-132-CM25</t>
         </is>
       </c>
-      <c r="B312" t="inlineStr">
-        <is>
-          <t>2239-13-LR23</t>
-        </is>
-      </c>
-      <c r="C312" t="inlineStr">
-        <is>
-          <t>ago-2025</t>
-        </is>
-      </c>
-      <c r="D312" t="inlineStr">
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
         <is>
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="E312" t="inlineStr">
+      <c r="E313" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F312" t="inlineStr">
+      <c r="F313" t="inlineStr">
         <is>
           <t>69.060.600-3</t>
         </is>
       </c>
-      <c r="G312" t="inlineStr">
+      <c r="G313" t="inlineStr">
         <is>
           <t>I MUNICIPALIDAD DE NOGALES</t>
         </is>
       </c>
-      <c r="H312" t="inlineStr">
+      <c r="H313" t="inlineStr">
         <is>
           <t>Valparaíso</t>
         </is>
       </c>
-      <c r="I312" t="inlineStr">
-        <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
-        </is>
-      </c>
-      <c r="J312" t="inlineStr">
-        <is>
-          <t>96.781.350-8</t>
-        </is>
-      </c>
-      <c r="K312" t="inlineStr"/>
-      <c r="L312" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M312" s="2" t="n">
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M313" s="2" t="n">
         <v>13116.14</v>
       </c>
     </row>
